--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Orti urbani.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Orti urbani.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="126">
   <si>
     <r>
       <t xml:space="preserve">
@@ -171,7 +171,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi bandi in corso</t>
+    <t>Vai ai bandi aperti</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -455,7 +455,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo presente un allegato]</t>
     </r>
     <r>
       <rPr>
@@ -582,7 +582,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -940,8 +940,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">.
-Per richiedere il rinnovo, [visita questo sito](URL).</t>
+      <t>.</t>
     </r>
   </si>
   <si>
@@ -1163,7 +1162,7 @@
     </r>
   </si>
   <si>
-    <t>n/a</t>
+    <t>Fai domanda</t>
   </si>
   <si>
     <t>Vai alla graduatoria</t>
@@ -1173,6 +1172,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Richiedi il rinnovo</t>
   </si>
   <si>
     <r>
@@ -1188,23 +1190,23 @@
     </r>
   </si>
   <si>
-    <t>**📎 **Allegato Premium: &lt;testo integrale del bando&gt;</t>
-  </si>
-  <si>
-    <t>**📎 **Allegato Premium: &lt;regolamento&gt;</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
       <t xml:space="preserve">
 File allegato al messaggio</t>
     </r>
+  </si>
+  <si>
+    <t>&lt;testo integrale del bando&gt;</t>
+  </si>
+  <si>
+    <t>&lt;regolamento&gt;</t>
   </si>
   <si>
     <r>
@@ -1287,18 +1289,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -2072,7 +2062,7 @@
         <v>98</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6" s="34" t="s">
         <v>99</v>
@@ -2087,7 +2077,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J6" s="34" t="s">
         <v>100</v>
@@ -2101,16 +2091,16 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="E7" s="34" t="s">
         <v>61</v>
@@ -2139,16 +2129,16 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>100</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E8" s="34" t="s">
         <v>100</v>
@@ -2177,101 +2167,101 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L10" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>61</v>
